--- a/result/Table202506.xlsx
+++ b/result/Table202506.xlsx
@@ -516,24 +516,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="I2" t="n">
         <v>15.42</v>
       </c>
       <c r="J2" t="n">
-        <v>14.03</v>
+        <v>16.1</v>
       </c>
       <c r="K2" t="n">
-        <v>-9.01</v>
+        <v>4.41</v>
       </c>
       <c r="L2" t="n">
-        <v>-9014.27</v>
+        <v>4409.86</v>
       </c>
     </row>
     <row r="3">
@@ -562,24 +562,24 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I3" t="n">
         <v>3.75</v>
       </c>
       <c r="J3" t="n">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="K3" t="n">
-        <v>6.93</v>
+        <v>7.73</v>
       </c>
       <c r="L3" t="n">
-        <v>6933.33</v>
+        <v>7733.33</v>
       </c>
     </row>
     <row r="4">
@@ -658,24 +658,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>15.41</v>
       </c>
       <c r="J5" t="n">
-        <v>14.78</v>
+        <v>13.99</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.09</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-4088.25</v>
+        <v>-9214.799999999999</v>
       </c>
     </row>
     <row r="6">
@@ -804,24 +804,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
         <v>23.5</v>
       </c>
       <c r="J8" t="n">
-        <v>22.4</v>
+        <v>20.71</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.68</v>
+        <v>-11.87</v>
       </c>
       <c r="L8" t="n">
-        <v>-4680.85</v>
+        <v>-11872.34</v>
       </c>
     </row>
     <row r="9">
@@ -900,24 +900,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="I10" t="n">
         <v>17.47</v>
       </c>
       <c r="J10" t="n">
-        <v>16.46</v>
+        <v>22.32</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.78</v>
+        <v>27.76</v>
       </c>
       <c r="L10" t="n">
-        <v>-5781.34</v>
+        <v>27761.88</v>
       </c>
     </row>
     <row r="11">
@@ -946,24 +946,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
         <v>38.81</v>
       </c>
       <c r="J11" t="n">
-        <v>36.4</v>
+        <v>34.26</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.21</v>
+        <v>-11.72</v>
       </c>
       <c r="L11" t="n">
-        <v>-6209.74</v>
+        <v>-11723.78</v>
       </c>
     </row>
     <row r="12">
@@ -992,24 +992,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>39</v>
       </c>
       <c r="J12" t="n">
-        <v>36.73</v>
+        <v>34.8</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.82</v>
+        <v>-10.77</v>
       </c>
       <c r="L12" t="n">
-        <v>-5820.51</v>
+        <v>-10769.23</v>
       </c>
     </row>
     <row r="13">
@@ -1088,24 +1088,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I14" t="n">
         <v>33.38</v>
       </c>
       <c r="J14" t="n">
-        <v>31.7</v>
+        <v>29.87</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.03</v>
+        <v>-10.52</v>
       </c>
       <c r="L14" t="n">
-        <v>-5032.95</v>
+        <v>-10515.28</v>
       </c>
     </row>
     <row r="15">
@@ -1234,24 +1234,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I17" t="n">
         <v>9.93</v>
       </c>
       <c r="J17" t="n">
-        <v>10.49</v>
+        <v>10.18</v>
       </c>
       <c r="K17" t="n">
-        <v>5.64</v>
+        <v>2.52</v>
       </c>
       <c r="L17" t="n">
-        <v>5639.48</v>
+        <v>2517.62</v>
       </c>
     </row>
     <row r="18">
@@ -1376,24 +1376,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I20" t="n">
         <v>8.539999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>8.17</v>
+        <v>8.82</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.33</v>
+        <v>3.28</v>
       </c>
       <c r="L20" t="n">
-        <v>-4332.55</v>
+        <v>3278.69</v>
       </c>
     </row>
     <row r="21">
@@ -1572,24 +1572,24 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I24" t="n">
         <v>7.52</v>
       </c>
       <c r="J24" t="n">
-        <v>8.9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>18.35</v>
+        <v>14.89</v>
       </c>
       <c r="L24" t="n">
-        <v>18351.06</v>
+        <v>14893.62</v>
       </c>
     </row>
     <row r="25">
@@ -1618,24 +1618,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="I25" t="n">
         <v>27.93</v>
       </c>
       <c r="J25" t="n">
-        <v>27.66</v>
+        <v>46.09</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.97</v>
+        <v>65.02</v>
       </c>
       <c r="L25" t="n">
-        <v>-966.7</v>
+        <v>65019.69</v>
       </c>
     </row>
     <row r="26">
@@ -1714,24 +1714,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I27" t="n">
         <v>33.16</v>
       </c>
       <c r="J27" t="n">
-        <v>30.11</v>
+        <v>29.36</v>
       </c>
       <c r="K27" t="n">
-        <v>-9.199999999999999</v>
+        <v>-11.46</v>
       </c>
       <c r="L27" t="n">
-        <v>-9197.83</v>
+        <v>-11459.59</v>
       </c>
     </row>
   </sheetData>
